--- a/Client/Tables/G_ItemInfoTable.xlsx
+++ b/Client/Tables/G_ItemInfoTable.xlsx
@@ -25021,9 +25021,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -34919,12 +34916,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
-    <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -44814,10 +44805,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -54707,10 +54694,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
